--- a/test/cus.xlsx
+++ b/test/cus.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65BC31A5-80F0-4A76-B3CC-1F88655159F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845166FF-DEC9-49E0-8F9F-E6F5002B3048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,15 +58,6 @@
     <t>GST345678</t>
   </si>
   <si>
-    <t>PAN1234567</t>
-  </si>
-  <si>
-    <t>PAN2345678</t>
-  </si>
-  <si>
-    <t>PAN3456789</t>
-  </si>
-  <si>
     <t>123 Street, City</t>
   </si>
   <si>
@@ -85,13 +76,22 @@
     <t>michael@example.com</t>
   </si>
   <si>
-    <t>aaaa</t>
-  </si>
-  <si>
-    <t>bbbb</t>
-  </si>
-  <si>
-    <t>cccc</t>
+    <t>ASDFF7412L</t>
+  </si>
+  <si>
+    <t>QWERT5678Y</t>
+  </si>
+  <si>
+    <t>ZXCVB7890I</t>
+  </si>
+  <si>
+    <t>Kirti</t>
+  </si>
+  <si>
+    <t>Vaishnavi</t>
+  </si>
+  <si>
+    <t>Oyami</t>
   </si>
 </sst>
 </file>
@@ -461,6 +461,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -499,10 +502,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -514,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I2">
         <v>9876543210</v>
@@ -528,10 +531,10 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -543,7 +546,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I3">
         <v>8765432109</v>
@@ -557,10 +560,10 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
         <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -572,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I4">
         <v>7654321098</v>
